--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -19,54 +19,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Ice</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Fire</x:t>
   </x:si>
   <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전방으로 불을 뿜는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
   </x:si>
   <x:si>
     <x:t>아이스</x:t>
@@ -75,37 +90,37 @@
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>_skillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>_skillCoolTime</x:t>
   </x:si>
   <x:si>
     <x:t>skill_fire_01</x:t>
   </x:si>
   <x:si>
-    <x:t>_skillDistance</x:t>
-  </x:si>
-  <x:si>
     <x:t>마법으로 만든 화살을 날린다</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>_skillCoolTime</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_ice_01</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
+    <x:t>Anim/AnimController_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Fire</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -879,11 +894,12 @@
     <x:col min="6" max="6" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
     <x:col min="7" max="7" width="14.0625" style="1" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="15.0703125" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="9" max="9" width="31.609375" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -892,71 +908,78 @@
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2"/>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I1" s="2"/>
+    </x:row>
+    <x:row r="2" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A3" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A3" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
@@ -970,7 +993,9 @@
       <x:c r="H4" s="5">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I4" s="4"/>
+      <x:c r="I4" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
@@ -981,16 +1006,16 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>1</x:v>
@@ -1004,7 +1029,9 @@
       <x:c r="H5" s="6">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I5" s="4"/>
+      <x:c r="I5" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="J5" s="4"/>
       <x:c r="K5" s="4"/>
       <x:c r="L5" s="4"/>
@@ -1015,16 +1042,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="s">
+      <x:c r="D6" s="6" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>1</x:v>
@@ -1038,7 +1065,9 @@
       <x:c r="H6" s="6">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I6" s="4"/>
+      <x:c r="I6" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="J6" s="4"/>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
@@ -1049,16 +1078,16 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>1</x:v>
@@ -1072,7 +1101,9 @@
       <x:c r="H7" s="7">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I7" s="4"/>
+      <x:c r="I7" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>
       <x:c r="L7" s="4"/>
@@ -1090,7 +1121,7 @@
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7"/>
-      <x:c r="I8" s="4"/>
+      <x:c r="I8" s="7"/>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4"/>
@@ -1108,7 +1139,7 @@
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6"/>
       <x:c r="H9" s="6"/>
-      <x:c r="I9" s="4"/>
+      <x:c r="I9" s="6"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
       <x:c r="L9" s="4"/>
@@ -1126,7 +1157,7 @@
       <x:c r="F10" s="5"/>
       <x:c r="G10" s="5"/>
       <x:c r="H10" s="5"/>
-      <x:c r="I10" s="4"/>
+      <x:c r="I10" s="5"/>
       <x:c r="J10" s="4"/>
       <x:c r="K10" s="4"/>
       <x:c r="L10" s="4"/>
@@ -1144,7 +1175,7 @@
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7"/>
-      <x:c r="I11" s="4"/>
+      <x:c r="I11" s="7"/>
       <x:c r="J11" s="4"/>
       <x:c r="K11" s="4"/>
       <x:c r="L11" s="4"/>
@@ -1162,7 +1193,7 @@
       <x:c r="F12" s="7"/>
       <x:c r="G12" s="7"/>
       <x:c r="H12" s="7"/>
-      <x:c r="I12" s="4"/>
+      <x:c r="I12" s="7"/>
       <x:c r="J12" s="4"/>
       <x:c r="K12" s="4"/>
       <x:c r="L12" s="4"/>
@@ -1171,7 +1202,7 @@
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
     </x:row>
-    <x:row r="13" spans="1:8" ht="15.75" customHeight="1">
+    <x:row r="13" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A13" s="8"/>
       <x:c r="B13" s="8"/>
       <x:c r="C13" s="8"/>
@@ -1180,8 +1211,9 @@
       <x:c r="F13" s="8"/>
       <x:c r="G13" s="8"/>
       <x:c r="H13" s="8"/>
-    </x:row>
-    <x:row r="14" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I13" s="8"/>
+    </x:row>
+    <x:row r="14" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A14" s="9"/>
       <x:c r="B14" s="9"/>
       <x:c r="C14" s="9"/>
@@ -1190,8 +1222,9 @@
       <x:c r="F14" s="8"/>
       <x:c r="G14" s="8"/>
       <x:c r="H14" s="8"/>
-    </x:row>
-    <x:row r="15" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I14" s="8"/>
+    </x:row>
+    <x:row r="15" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A15" s="9"/>
       <x:c r="B15" s="9"/>
       <x:c r="C15" s="9"/>
@@ -1200,8 +1233,9 @@
       <x:c r="F15" s="8"/>
       <x:c r="G15" s="8"/>
       <x:c r="H15" s="8"/>
-    </x:row>
-    <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I15" s="8"/>
+    </x:row>
+    <x:row r="16" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A16" s="9"/>
       <x:c r="B16" s="9"/>
       <x:c r="C16" s="9"/>
@@ -1210,8 +1244,9 @@
       <x:c r="F16" s="8"/>
       <x:c r="G16" s="8"/>
       <x:c r="H16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I16" s="8"/>
+    </x:row>
+    <x:row r="17" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A17" s="9"/>
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="9"/>
@@ -1220,8 +1255,9 @@
       <x:c r="F17" s="8"/>
       <x:c r="G17" s="8"/>
       <x:c r="H17" s="8"/>
-    </x:row>
-    <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I17" s="8"/>
+    </x:row>
+    <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="9"/>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
@@ -1230,8 +1266,9 @@
       <x:c r="F18" s="8"/>
       <x:c r="G18" s="8"/>
       <x:c r="H18" s="8"/>
-    </x:row>
-    <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
@@ -1240,8 +1277,9 @@
       <x:c r="F19" s="8"/>
       <x:c r="G19" s="8"/>
       <x:c r="H19" s="8"/>
-    </x:row>
-    <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I19" s="8"/>
+    </x:row>
+    <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A20" s="9"/>
       <x:c r="B20" s="9"/>
       <x:c r="C20" s="9"/>
@@ -1250,8 +1288,9 @@
       <x:c r="F20" s="8"/>
       <x:c r="G20" s="8"/>
       <x:c r="H20" s="8"/>
-    </x:row>
-    <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I20" s="8"/>
+    </x:row>
+    <x:row r="21" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A21" s="9"/>
       <x:c r="B21" s="9"/>
       <x:c r="C21" s="9"/>
@@ -1260,8 +1299,9 @@
       <x:c r="F21" s="8"/>
       <x:c r="G21" s="8"/>
       <x:c r="H21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I21" s="8"/>
+    </x:row>
+    <x:row r="22" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A22" s="9"/>
       <x:c r="B22" s="9"/>
       <x:c r="C22" s="9"/>
@@ -1270,8 +1310,9 @@
       <x:c r="F22" s="8"/>
       <x:c r="G22" s="8"/>
       <x:c r="H22" s="8"/>
-    </x:row>
-    <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I22" s="8"/>
+    </x:row>
+    <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A23" s="10"/>
       <x:c r="B23" s="10"/>
       <x:c r="C23" s="10"/>
@@ -1280,8 +1321,9 @@
       <x:c r="F23" s="10"/>
       <x:c r="G23" s="10"/>
       <x:c r="H23" s="10"/>
-    </x:row>
-    <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I23" s="10"/>
+    </x:row>
+    <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A24" s="10"/>
       <x:c r="B24" s="10"/>
       <x:c r="C24" s="10"/>
@@ -1290,8 +1332,9 @@
       <x:c r="F24" s="10"/>
       <x:c r="G24" s="10"/>
       <x:c r="H24" s="10"/>
-    </x:row>
-    <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I24" s="10"/>
+    </x:row>
+    <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A25" s="10"/>
       <x:c r="B25" s="10"/>
       <x:c r="C25" s="10"/>
@@ -1300,8 +1343,9 @@
       <x:c r="F25" s="10"/>
       <x:c r="G25" s="10"/>
       <x:c r="H25" s="10"/>
-    </x:row>
-    <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I25" s="10"/>
+    </x:row>
+    <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A26" s="10"/>
       <x:c r="B26" s="10"/>
       <x:c r="C26" s="10"/>
@@ -1310,8 +1354,9 @@
       <x:c r="F26" s="10"/>
       <x:c r="G26" s="10"/>
       <x:c r="H26" s="10"/>
-    </x:row>
-    <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I26" s="10"/>
+    </x:row>
+    <x:row r="27" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A27" s="10"/>
       <x:c r="B27" s="10"/>
       <x:c r="C27" s="10"/>
@@ -1320,8 +1365,9 @@
       <x:c r="F27" s="10"/>
       <x:c r="G27" s="10"/>
       <x:c r="H27" s="10"/>
-    </x:row>
-    <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I27" s="10"/>
+    </x:row>
+    <x:row r="28" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A28" s="10"/>
       <x:c r="B28" s="10"/>
       <x:c r="C28" s="10"/>
@@ -1330,8 +1376,9 @@
       <x:c r="F28" s="10"/>
       <x:c r="G28" s="10"/>
       <x:c r="H28" s="10"/>
-    </x:row>
-    <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I28" s="10"/>
+    </x:row>
+    <x:row r="29" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A29" s="11"/>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="11"/>
@@ -1340,8 +1387,9 @@
       <x:c r="F29" s="11"/>
       <x:c r="G29" s="11"/>
       <x:c r="H29" s="11"/>
-    </x:row>
-    <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I29" s="11"/>
+    </x:row>
+    <x:row r="30" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A30" s="11"/>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="11"/>
@@ -1350,8 +1398,9 @@
       <x:c r="F30" s="11"/>
       <x:c r="G30" s="11"/>
       <x:c r="H30" s="11"/>
-    </x:row>
-    <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I30" s="11"/>
+    </x:row>
+    <x:row r="31" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A31" s="11"/>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="11"/>
@@ -1360,8 +1409,9 @@
       <x:c r="F31" s="11"/>
       <x:c r="G31" s="11"/>
       <x:c r="H31" s="11"/>
-    </x:row>
-    <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I31" s="11"/>
+    </x:row>
+    <x:row r="32" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A32" s="11"/>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="11"/>
@@ -1370,6 +1420,7 @@
       <x:c r="F32" s="11"/>
       <x:c r="G32" s="11"/>
       <x:c r="H32" s="11"/>
+      <x:c r="I32" s="11"/>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1"/>
     <x:row r="34" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -19,105 +19,126 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
+  </x:si>
   <x:si>
     <x:t>Anim/AnimController_Lightning</x:t>
   </x:si>
   <x:si>
-    <x:t>전방으로 불을 뿜는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>Anim/AnimController_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법으로 만든 화살을 날린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDuration</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Lightning</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>_skillDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>_skillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Ice</x:t>
   </x:si>
   <x:si>
     <x:t>Anim/AnimController_Fire</x:t>
@@ -895,91 +916,117 @@
     <x:col min="7" max="7" width="14.0625" style="1" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="15.0703125" style="1" bestFit="1" customWidth="1"/>
     <x:col min="9" max="9" width="31.609375" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="10" max="10" width="15.0703125" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="11" max="11" width="19.91015625" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
-      <x:c r="G1" s="2"/>
-      <x:c r="H1" s="2"/>
-      <x:c r="I1" s="2"/>
-    </x:row>
-    <x:row r="2" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="G1" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A3" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="s">
+      <x:c r="D3" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
+      <x:c r="F3" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A3" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
@@ -994,10 +1041,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="J4" s="4"/>
-      <x:c r="K4" s="4"/>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J4" s="5"/>
+      <x:c r="K4" s="5"/>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
       <x:c r="N4" s="4"/>
@@ -1006,16 +1053,16 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>1</x:v>
@@ -1030,10 +1077,14 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="J5" s="4"/>
-      <x:c r="K5" s="4"/>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J5" s="6">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="K5" s="6">
+        <x:v>1.2</x:v>
+      </x:c>
       <x:c r="L5" s="4"/>
       <x:c r="M5" s="4"/>
       <x:c r="N5" s="4"/>
@@ -1042,16 +1093,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>1</x:v>
@@ -1066,10 +1117,12 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="J6" s="4"/>
-      <x:c r="K6" s="4"/>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J6" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K6" s="6"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
       <x:c r="N6" s="4"/>
@@ -1078,16 +1131,16 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>1</x:v>
@@ -1102,10 +1155,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="4"/>
-      <x:c r="K7" s="4"/>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J7" s="7"/>
+      <x:c r="K7" s="7"/>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
       <x:c r="N7" s="4"/>
@@ -1122,8 +1175,8 @@
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="7"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
+      <x:c r="J8" s="7"/>
+      <x:c r="K8" s="7"/>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
       <x:c r="N8" s="4"/>
@@ -1140,8 +1193,8 @@
       <x:c r="G9" s="6"/>
       <x:c r="H9" s="6"/>
       <x:c r="I9" s="6"/>
-      <x:c r="J9" s="4"/>
-      <x:c r="K9" s="4"/>
+      <x:c r="J9" s="6"/>
+      <x:c r="K9" s="6"/>
       <x:c r="L9" s="4"/>
       <x:c r="M9" s="4"/>
       <x:c r="N9" s="4"/>
@@ -1158,8 +1211,8 @@
       <x:c r="G10" s="5"/>
       <x:c r="H10" s="5"/>
       <x:c r="I10" s="5"/>
-      <x:c r="J10" s="4"/>
-      <x:c r="K10" s="4"/>
+      <x:c r="J10" s="5"/>
+      <x:c r="K10" s="5"/>
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="4"/>
       <x:c r="N10" s="4"/>
@@ -1176,8 +1229,8 @@
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="7"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
+      <x:c r="J11" s="7"/>
+      <x:c r="K11" s="7"/>
       <x:c r="L11" s="4"/>
       <x:c r="M11" s="4"/>
       <x:c r="N11" s="4"/>
@@ -1194,15 +1247,15 @@
       <x:c r="G12" s="7"/>
       <x:c r="H12" s="7"/>
       <x:c r="I12" s="7"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
+      <x:c r="J12" s="7"/>
+      <x:c r="K12" s="7"/>
       <x:c r="L12" s="4"/>
       <x:c r="M12" s="4"/>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
     </x:row>
-    <x:row r="13" spans="1:9" ht="15.75" customHeight="1">
+    <x:row r="13" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A13" s="8"/>
       <x:c r="B13" s="8"/>
       <x:c r="C13" s="8"/>
@@ -1212,8 +1265,10 @@
       <x:c r="G13" s="8"/>
       <x:c r="H13" s="8"/>
       <x:c r="I13" s="8"/>
-    </x:row>
-    <x:row r="14" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J13" s="8"/>
+      <x:c r="K13" s="8"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A14" s="9"/>
       <x:c r="B14" s="9"/>
       <x:c r="C14" s="9"/>
@@ -1223,8 +1278,10 @@
       <x:c r="G14" s="8"/>
       <x:c r="H14" s="8"/>
       <x:c r="I14" s="8"/>
-    </x:row>
-    <x:row r="15" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J14" s="8"/>
+      <x:c r="K14" s="8"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A15" s="9"/>
       <x:c r="B15" s="9"/>
       <x:c r="C15" s="9"/>
@@ -1234,8 +1291,10 @@
       <x:c r="G15" s="8"/>
       <x:c r="H15" s="8"/>
       <x:c r="I15" s="8"/>
-    </x:row>
-    <x:row r="16" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J15" s="8"/>
+      <x:c r="K15" s="8"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A16" s="9"/>
       <x:c r="B16" s="9"/>
       <x:c r="C16" s="9"/>
@@ -1245,8 +1304,10 @@
       <x:c r="G16" s="8"/>
       <x:c r="H16" s="8"/>
       <x:c r="I16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J16" s="8"/>
+      <x:c r="K16" s="8"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A17" s="9"/>
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="9"/>
@@ -1256,8 +1317,10 @@
       <x:c r="G17" s="8"/>
       <x:c r="H17" s="8"/>
       <x:c r="I17" s="8"/>
-    </x:row>
-    <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J17" s="8"/>
+      <x:c r="K17" s="8"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A18" s="9"/>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
@@ -1267,8 +1330,10 @@
       <x:c r="G18" s="8"/>
       <x:c r="H18" s="8"/>
       <x:c r="I18" s="8"/>
-    </x:row>
-    <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J18" s="8"/>
+      <x:c r="K18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
@@ -1278,8 +1343,10 @@
       <x:c r="G19" s="8"/>
       <x:c r="H19" s="8"/>
       <x:c r="I19" s="8"/>
-    </x:row>
-    <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J19" s="8"/>
+      <x:c r="K19" s="8"/>
+    </x:row>
+    <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A20" s="9"/>
       <x:c r="B20" s="9"/>
       <x:c r="C20" s="9"/>
@@ -1289,8 +1356,10 @@
       <x:c r="G20" s="8"/>
       <x:c r="H20" s="8"/>
       <x:c r="I20" s="8"/>
-    </x:row>
-    <x:row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J20" s="8"/>
+      <x:c r="K20" s="8"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A21" s="9"/>
       <x:c r="B21" s="9"/>
       <x:c r="C21" s="9"/>
@@ -1300,8 +1369,10 @@
       <x:c r="G21" s="8"/>
       <x:c r="H21" s="8"/>
       <x:c r="I21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J21" s="8"/>
+      <x:c r="K21" s="8"/>
+    </x:row>
+    <x:row r="22" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A22" s="9"/>
       <x:c r="B22" s="9"/>
       <x:c r="C22" s="9"/>
@@ -1311,8 +1382,10 @@
       <x:c r="G22" s="8"/>
       <x:c r="H22" s="8"/>
       <x:c r="I22" s="8"/>
-    </x:row>
-    <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J22" s="8"/>
+      <x:c r="K22" s="8"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A23" s="10"/>
       <x:c r="B23" s="10"/>
       <x:c r="C23" s="10"/>
@@ -1322,8 +1395,10 @@
       <x:c r="G23" s="10"/>
       <x:c r="H23" s="10"/>
       <x:c r="I23" s="10"/>
-    </x:row>
-    <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J23" s="10"/>
+      <x:c r="K23" s="10"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A24" s="10"/>
       <x:c r="B24" s="10"/>
       <x:c r="C24" s="10"/>
@@ -1333,8 +1408,10 @@
       <x:c r="G24" s="10"/>
       <x:c r="H24" s="10"/>
       <x:c r="I24" s="10"/>
-    </x:row>
-    <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J24" s="10"/>
+      <x:c r="K24" s="10"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A25" s="10"/>
       <x:c r="B25" s="10"/>
       <x:c r="C25" s="10"/>
@@ -1344,8 +1421,10 @@
       <x:c r="G25" s="10"/>
       <x:c r="H25" s="10"/>
       <x:c r="I25" s="10"/>
-    </x:row>
-    <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J25" s="10"/>
+      <x:c r="K25" s="10"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A26" s="10"/>
       <x:c r="B26" s="10"/>
       <x:c r="C26" s="10"/>
@@ -1355,8 +1434,10 @@
       <x:c r="G26" s="10"/>
       <x:c r="H26" s="10"/>
       <x:c r="I26" s="10"/>
-    </x:row>
-    <x:row r="27" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J26" s="10"/>
+      <x:c r="K26" s="10"/>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A27" s="10"/>
       <x:c r="B27" s="10"/>
       <x:c r="C27" s="10"/>
@@ -1366,8 +1447,10 @@
       <x:c r="G27" s="10"/>
       <x:c r="H27" s="10"/>
       <x:c r="I27" s="10"/>
-    </x:row>
-    <x:row r="28" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J27" s="10"/>
+      <x:c r="K27" s="10"/>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A28" s="10"/>
       <x:c r="B28" s="10"/>
       <x:c r="C28" s="10"/>
@@ -1377,8 +1460,10 @@
       <x:c r="G28" s="10"/>
       <x:c r="H28" s="10"/>
       <x:c r="I28" s="10"/>
-    </x:row>
-    <x:row r="29" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J28" s="10"/>
+      <x:c r="K28" s="10"/>
+    </x:row>
+    <x:row r="29" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A29" s="11"/>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="11"/>
@@ -1388,8 +1473,10 @@
       <x:c r="G29" s="11"/>
       <x:c r="H29" s="11"/>
       <x:c r="I29" s="11"/>
-    </x:row>
-    <x:row r="30" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J29" s="11"/>
+      <x:c r="K29" s="11"/>
+    </x:row>
+    <x:row r="30" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A30" s="11"/>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="11"/>
@@ -1399,8 +1486,10 @@
       <x:c r="G30" s="11"/>
       <x:c r="H30" s="11"/>
       <x:c r="I30" s="11"/>
-    </x:row>
-    <x:row r="31" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J30" s="11"/>
+      <x:c r="K30" s="11"/>
+    </x:row>
+    <x:row r="31" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A31" s="11"/>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="11"/>
@@ -1410,8 +1499,10 @@
       <x:c r="G31" s="11"/>
       <x:c r="H31" s="11"/>
       <x:c r="I31" s="11"/>
-    </x:row>
-    <x:row r="32" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J31" s="11"/>
+      <x:c r="K31" s="11"/>
+    </x:row>
+    <x:row r="32" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A32" s="11"/>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="11"/>
@@ -1421,6 +1512,8 @@
       <x:c r="G32" s="11"/>
       <x:c r="H32" s="11"/>
       <x:c r="I32" s="11"/>
+      <x:c r="J32" s="11"/>
+      <x:c r="K32" s="11"/>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1"/>
     <x:row r="34" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -21,127 +21,127 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <x:si>
+    <x:t>마법으로 만든 화살을 날린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
     <x:t>매직애로우</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
     <x:t>라이트닝</x:t>
   </x:si>
   <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>전방으로 불을 뿜는다</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
     <x:t>SkillDamage</x:t>
   </x:si>
   <x:si>
     <x:t>SkillLevel</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
+  </x:si>
+  <x:si>
     <x:t>Anim/AnimController_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Fire</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -922,7 +922,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -930,103 +930,103 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="J3" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K3" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
@@ -1041,7 +1041,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
@@ -1053,13 +1053,13 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
         <x:v>21</x:v>
@@ -1077,7 +1077,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J5" s="6">
         <x:v>1.5</x:v>
@@ -1093,16 +1093,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>1</x:v>
@@ -1117,7 +1117,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J6" s="6">
         <x:v>1</x:v>
@@ -1131,16 +1131,16 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>1</x:v>
@@ -1155,7 +1155,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -21,79 +21,112 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
     <x:t>마법으로 만든 화살을 날린다</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDistance</x:t>
+    <x:t>Anim/AnimController_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>float</x:t>
   </x:si>
   <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
     <x:t>스킬 지속시간</x:t>
   </x:si>
   <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
+    <x:t>Anim/AnimController_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
   </x:si>
   <x:si>
     <x:t>skill_magicArrow_01</x:t>
@@ -102,46 +135,13 @@
     <x:t>SkillDamageInterval</x:t>
   </x:si>
   <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전방으로 불을 뿜는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_MagicArrow</x:t>
   </x:si>
   <x:si>
     <x:t>Anim/AnimController_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Ice</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -922,7 +922,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -930,54 +930,54 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11" ht="15.75" customHeight="1">
@@ -985,48 +985,48 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K3" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
@@ -1041,7 +1041,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
@@ -1053,16 +1053,16 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>1</x:v>
@@ -1077,7 +1077,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J5" s="6">
         <x:v>1.5</x:v>
@@ -1093,16 +1093,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>1</x:v>
@@ -1117,7 +1117,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J6" s="6">
         <x:v>1</x:v>
@@ -1131,16 +1131,16 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>1</x:v>
@@ -1155,7 +1155,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -19,129 +19,126 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법으로 만든 화살을 날린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
   <x:si>
     <x:t>skill_lightning_01</x:t>
   </x:si>
   <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전방으로 불을 뿜는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Fire</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
+    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
   </x:si>
   <x:si>
     <x:t>Anim/AnimController_MagicArrow</x:t>
   </x:si>
   <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Fire</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Fire</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -922,7 +919,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -930,103 +927,103 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
+      <x:c r="I3" s="3" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
+      <x:c r="J3" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K3" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
@@ -1041,7 +1038,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
@@ -1053,19 +1050,19 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E5" s="6">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="6">
         <x:v>200</x:v>
@@ -1077,7 +1074,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J5" s="6">
         <x:v>1.5</x:v>
@@ -1093,19 +1090,19 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E6" s="6">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="6">
         <x:v>100</x:v>
@@ -1116,9 +1113,7 @@
       <x:c r="H6" s="6">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I6" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
+      <x:c r="I6" s="5"/>
       <x:c r="J6" s="6">
         <x:v>1</x:v>
       </x:c>
@@ -1131,19 +1126,19 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D7" s="7" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E7" s="7">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D7" s="7" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E7" s="7">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="7">
         <x:v>150</x:v>
@@ -1155,7 +1150,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -19,119 +19,119 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
   <x:si>
     <x:t>스킬애니메이션경로</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전방으로 불을 뿜는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
   </x:si>
   <x:si>
     <x:t>사거리</x:t>
   </x:si>
   <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
     <x:t>아이스</x:t>
   </x:si>
   <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_ice_01</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법으로 만든 화살을 날린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다</x:t>
+  </x:si>
+  <x:si>
     <x:t>SkillDuration</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_MagicArrow</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_MagicArrow</x:t>
   </x:si>
   <x:si>
@@ -139,6 +139,18 @@
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolDownPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 데미지 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamagePerLevel</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -915,11 +927,13 @@
     <x:col min="9" max="9" width="31.609375" style="1" bestFit="1" customWidth="1"/>
     <x:col min="10" max="10" width="15.0703125" style="1" bestFit="1" customWidth="1"/>
     <x:col min="11" max="11" width="19.91015625" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="12" max="12" width="22.26953125" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="13" width="24.18359375" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -927,100 +941,118 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M1" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A2" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="B2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="M2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A3" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A2" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K2" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A3" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J3" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K3" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L3" s="3" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="M3" s="3" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
         <x:v>37</x:v>
@@ -1038,28 +1070,32 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
-      <x:c r="L4" s="4"/>
-      <x:c r="M4" s="4"/>
+      <x:c r="L4" s="5">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="M4" s="5">
+        <x:v>0.20000000000000001</x:v>
+      </x:c>
       <x:c r="N4" s="4"/>
       <x:c r="O4" s="4"/>
       <x:c r="P4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>0</x:v>
@@ -1082,24 +1118,28 @@
       <x:c r="K5" s="6">
         <x:v>1.2</x:v>
       </x:c>
-      <x:c r="L5" s="4"/>
-      <x:c r="M5" s="4"/>
+      <x:c r="L5" s="5">
+        <x:v>0.29999999999999999</x:v>
+      </x:c>
+      <x:c r="M5" s="6">
+        <x:v>0.29999999999999999</x:v>
+      </x:c>
       <x:c r="N5" s="4"/>
       <x:c r="O5" s="4"/>
       <x:c r="P5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>0</x:v>
@@ -1118,21 +1158,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K6" s="6"/>
-      <x:c r="L6" s="4"/>
-      <x:c r="M6" s="4"/>
+      <x:c r="L6" s="5">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="M6" s="6">
+        <x:v>0.20000000000000001</x:v>
+      </x:c>
       <x:c r="N6" s="4"/>
       <x:c r="O6" s="4"/>
       <x:c r="P6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
         <x:v>39</x:v>
@@ -1150,12 +1194,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>
-      <x:c r="L7" s="4"/>
-      <x:c r="M7" s="4"/>
+      <x:c r="L7" s="5">
+        <x:v>0.29999999999999999</x:v>
+      </x:c>
+      <x:c r="M7" s="7">
+        <x:v>0.20000000000000001</x:v>
+      </x:c>
       <x:c r="N7" s="4"/>
       <x:c r="O7" s="4"/>
       <x:c r="P7" s="4"/>
@@ -1172,8 +1220,8 @@
       <x:c r="I8" s="7"/>
       <x:c r="J8" s="7"/>
       <x:c r="K8" s="7"/>
-      <x:c r="L8" s="4"/>
-      <x:c r="M8" s="4"/>
+      <x:c r="L8" s="7"/>
+      <x:c r="M8" s="7"/>
       <x:c r="N8" s="4"/>
       <x:c r="O8" s="4"/>
       <x:c r="P8" s="4"/>
@@ -1190,8 +1238,8 @@
       <x:c r="I9" s="6"/>
       <x:c r="J9" s="6"/>
       <x:c r="K9" s="6"/>
-      <x:c r="L9" s="4"/>
-      <x:c r="M9" s="4"/>
+      <x:c r="L9" s="6"/>
+      <x:c r="M9" s="6"/>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="4"/>
       <x:c r="P9" s="4"/>
@@ -1208,8 +1256,8 @@
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5"/>
       <x:c r="K10" s="5"/>
-      <x:c r="L10" s="4"/>
-      <x:c r="M10" s="4"/>
+      <x:c r="L10" s="5"/>
+      <x:c r="M10" s="5"/>
       <x:c r="N10" s="4"/>
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
@@ -1226,8 +1274,8 @@
       <x:c r="I11" s="7"/>
       <x:c r="J11" s="7"/>
       <x:c r="K11" s="7"/>
-      <x:c r="L11" s="4"/>
-      <x:c r="M11" s="4"/>
+      <x:c r="L11" s="7"/>
+      <x:c r="M11" s="7"/>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
@@ -1244,13 +1292,13 @@
       <x:c r="I12" s="7"/>
       <x:c r="J12" s="7"/>
       <x:c r="K12" s="7"/>
-      <x:c r="L12" s="4"/>
-      <x:c r="M12" s="4"/>
+      <x:c r="L12" s="7"/>
+      <x:c r="M12" s="7"/>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
     </x:row>
-    <x:row r="13" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="8"/>
       <x:c r="B13" s="8"/>
       <x:c r="C13" s="8"/>
@@ -1262,8 +1310,10 @@
       <x:c r="I13" s="8"/>
       <x:c r="J13" s="8"/>
       <x:c r="K13" s="8"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L13" s="8"/>
+      <x:c r="M13" s="8"/>
+    </x:row>
+    <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="9"/>
       <x:c r="B14" s="9"/>
       <x:c r="C14" s="9"/>
@@ -1275,8 +1325,10 @@
       <x:c r="I14" s="8"/>
       <x:c r="J14" s="8"/>
       <x:c r="K14" s="8"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L14" s="8"/>
+      <x:c r="M14" s="8"/>
+    </x:row>
+    <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="9"/>
       <x:c r="B15" s="9"/>
       <x:c r="C15" s="9"/>
@@ -1288,8 +1340,10 @@
       <x:c r="I15" s="8"/>
       <x:c r="J15" s="8"/>
       <x:c r="K15" s="8"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L15" s="8"/>
+      <x:c r="M15" s="8"/>
+    </x:row>
+    <x:row r="16" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A16" s="9"/>
       <x:c r="B16" s="9"/>
       <x:c r="C16" s="9"/>
@@ -1301,8 +1355,10 @@
       <x:c r="I16" s="8"/>
       <x:c r="J16" s="8"/>
       <x:c r="K16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L16" s="8"/>
+      <x:c r="M16" s="8"/>
+    </x:row>
+    <x:row r="17" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A17" s="9"/>
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="9"/>
@@ -1314,8 +1370,10 @@
       <x:c r="I17" s="8"/>
       <x:c r="J17" s="8"/>
       <x:c r="K17" s="8"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L17" s="8"/>
+      <x:c r="M17" s="8"/>
+    </x:row>
+    <x:row r="18" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A18" s="9"/>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
@@ -1327,8 +1385,10 @@
       <x:c r="I18" s="8"/>
       <x:c r="J18" s="8"/>
       <x:c r="K18" s="8"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L18" s="8"/>
+      <x:c r="M18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
@@ -1340,8 +1400,10 @@
       <x:c r="I19" s="8"/>
       <x:c r="J19" s="8"/>
       <x:c r="K19" s="8"/>
-    </x:row>
-    <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L19" s="8"/>
+      <x:c r="M19" s="8"/>
+    </x:row>
+    <x:row r="20" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A20" s="9"/>
       <x:c r="B20" s="9"/>
       <x:c r="C20" s="9"/>
@@ -1353,8 +1415,10 @@
       <x:c r="I20" s="8"/>
       <x:c r="J20" s="8"/>
       <x:c r="K20" s="8"/>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L20" s="8"/>
+      <x:c r="M20" s="8"/>
+    </x:row>
+    <x:row r="21" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A21" s="9"/>
       <x:c r="B21" s="9"/>
       <x:c r="C21" s="9"/>
@@ -1366,8 +1430,10 @@
       <x:c r="I21" s="8"/>
       <x:c r="J21" s="8"/>
       <x:c r="K21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L21" s="8"/>
+      <x:c r="M21" s="8"/>
+    </x:row>
+    <x:row r="22" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A22" s="9"/>
       <x:c r="B22" s="9"/>
       <x:c r="C22" s="9"/>
@@ -1379,8 +1445,10 @@
       <x:c r="I22" s="8"/>
       <x:c r="J22" s="8"/>
       <x:c r="K22" s="8"/>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L22" s="8"/>
+      <x:c r="M22" s="8"/>
+    </x:row>
+    <x:row r="23" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A23" s="10"/>
       <x:c r="B23" s="10"/>
       <x:c r="C23" s="10"/>
@@ -1392,8 +1460,10 @@
       <x:c r="I23" s="10"/>
       <x:c r="J23" s="10"/>
       <x:c r="K23" s="10"/>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L23" s="10"/>
+      <x:c r="M23" s="10"/>
+    </x:row>
+    <x:row r="24" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A24" s="10"/>
       <x:c r="B24" s="10"/>
       <x:c r="C24" s="10"/>
@@ -1405,8 +1475,10 @@
       <x:c r="I24" s="10"/>
       <x:c r="J24" s="10"/>
       <x:c r="K24" s="10"/>
-    </x:row>
-    <x:row r="25" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L24" s="10"/>
+      <x:c r="M24" s="10"/>
+    </x:row>
+    <x:row r="25" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A25" s="10"/>
       <x:c r="B25" s="10"/>
       <x:c r="C25" s="10"/>
@@ -1418,8 +1490,10 @@
       <x:c r="I25" s="10"/>
       <x:c r="J25" s="10"/>
       <x:c r="K25" s="10"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L25" s="10"/>
+      <x:c r="M25" s="10"/>
+    </x:row>
+    <x:row r="26" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A26" s="10"/>
       <x:c r="B26" s="10"/>
       <x:c r="C26" s="10"/>
@@ -1431,8 +1505,10 @@
       <x:c r="I26" s="10"/>
       <x:c r="J26" s="10"/>
       <x:c r="K26" s="10"/>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L26" s="10"/>
+      <x:c r="M26" s="10"/>
+    </x:row>
+    <x:row r="27" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A27" s="10"/>
       <x:c r="B27" s="10"/>
       <x:c r="C27" s="10"/>
@@ -1444,8 +1520,10 @@
       <x:c r="I27" s="10"/>
       <x:c r="J27" s="10"/>
       <x:c r="K27" s="10"/>
-    </x:row>
-    <x:row r="28" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L27" s="10"/>
+      <x:c r="M27" s="10"/>
+    </x:row>
+    <x:row r="28" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A28" s="10"/>
       <x:c r="B28" s="10"/>
       <x:c r="C28" s="10"/>
@@ -1457,8 +1535,10 @@
       <x:c r="I28" s="10"/>
       <x:c r="J28" s="10"/>
       <x:c r="K28" s="10"/>
-    </x:row>
-    <x:row r="29" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L28" s="10"/>
+      <x:c r="M28" s="10"/>
+    </x:row>
+    <x:row r="29" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A29" s="11"/>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="11"/>
@@ -1470,8 +1550,10 @@
       <x:c r="I29" s="11"/>
       <x:c r="J29" s="11"/>
       <x:c r="K29" s="11"/>
-    </x:row>
-    <x:row r="30" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L29" s="11"/>
+      <x:c r="M29" s="11"/>
+    </x:row>
+    <x:row r="30" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A30" s="11"/>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="11"/>
@@ -1483,8 +1565,10 @@
       <x:c r="I30" s="11"/>
       <x:c r="J30" s="11"/>
       <x:c r="K30" s="11"/>
-    </x:row>
-    <x:row r="31" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L30" s="11"/>
+      <x:c r="M30" s="11"/>
+    </x:row>
+    <x:row r="31" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A31" s="11"/>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="11"/>
@@ -1496,8 +1580,10 @@
       <x:c r="I31" s="11"/>
       <x:c r="J31" s="11"/>
       <x:c r="K31" s="11"/>
-    </x:row>
-    <x:row r="32" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="L31" s="11"/>
+      <x:c r="M31" s="11"/>
+    </x:row>
+    <x:row r="32" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A32" s="11"/>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="11"/>
@@ -1509,6 +1595,8 @@
       <x:c r="I32" s="11"/>
       <x:c r="J32" s="11"/>
       <x:c r="K32" s="11"/>
+      <x:c r="L32" s="11"/>
+      <x:c r="M32" s="11"/>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1"/>
     <x:row r="34" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -21,94 +21,106 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <x:si>
+    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
     <x:t>SkillDamage</x:t>
   </x:si>
   <x:si>
-    <x:t>전방으로 불을 뿜는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
     <x:t>SkillLevel</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬애니메이션경로</x:t>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
+    <x:t>float</x:t>
   </x:si>
   <x:si>
     <x:t>스킬 지속시간</x:t>
   </x:si>
   <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolDownPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
   </x:si>
   <x:si>
     <x:t>파이어</x:t>
   </x:si>
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
     <x:t>사거리</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
+    <x:t>마법으로 만든 화살을 날린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
   </x:si>
   <x:si>
     <x:t>SkillCoolTime</x:t>
@@ -117,40 +129,28 @@
     <x:t>skill_ice_01</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다</x:t>
+    <x:t>스킬범위 안의 적들을 얼린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamagePerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDuration</x:t>
   </x:si>
   <x:si>
     <x:t>SkillDistance</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDuration</x:t>
+    <x:t>레벨당 오를 데미지 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Fire</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_MagicArrow</x:t>
   </x:si>
   <x:si>
-    <x:t>Anim/AnimController_Fire</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolDownPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 오를 데미지 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamagePerLevel</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -933,7 +933,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -941,107 +941,107 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="L1" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="M2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="I3" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L3" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M3" s="3" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L3" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="M3" s="3" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
@@ -1049,13 +1049,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
@@ -1070,7 +1070,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
@@ -1089,13 +1089,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>0</x:v>
@@ -1110,7 +1110,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J5" s="6">
         <x:v>1.5</x:v>
@@ -1130,16 +1130,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>0</x:v>
@@ -1170,16 +1170,16 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>0</x:v>
@@ -1194,7 +1194,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -19,7 +19,121 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolDownPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 데미지 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamagePerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법으로 만든 화살을 날린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다</x:t>
+  </x:si>
   <x:si>
     <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
   </x:si>
@@ -27,130 +141,13 @@
     <x:t>Anim/AnimController_Lightning</x:t>
   </x:si>
   <x:si>
-    <x:t>Anim/AnimController_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전방으로 불을 뿜는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolDownPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamagePerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 오를 데미지 수치</x:t>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
   </x:si>
   <x:si>
     <x:t>Anim/AnimController_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -933,7 +930,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -941,121 +938,121 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L1" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="M2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="J3" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K3" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L3" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M3" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
@@ -1069,13 +1066,11 @@
       <x:c r="H4" s="5">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I4" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5">
-        <x:v>0.5</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="M4" s="5">
         <x:v>0.20000000000000001</x:v>
@@ -1086,16 +1081,16 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>0</x:v>
@@ -1110,7 +1105,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J5" s="6">
         <x:v>1.5</x:v>
@@ -1119,7 +1114,7 @@
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="L5" s="5">
-        <x:v>0.29999999999999999</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="M5" s="6">
         <x:v>0.29999999999999999</x:v>
@@ -1130,13 +1125,13 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
         <x:v>20</x:v>
@@ -1159,7 +1154,7 @@
       </x:c>
       <x:c r="K6" s="6"/>
       <x:c r="L6" s="5">
-        <x:v>0.5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M6" s="6">
         <x:v>0.20000000000000001</x:v>
@@ -1170,16 +1165,16 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>0</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>0</x:v>
@@ -1194,12 +1189,12 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>
       <x:c r="L7" s="5">
-        <x:v>0.29999999999999999</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M7" s="7">
         <x:v>0.20000000000000001</x:v>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -19,128 +19,131 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolDownPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolDownPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다</x:t>
   </x:si>
   <x:si>
     <x:t>SkillCoolTime</x:t>
   </x:si>
   <x:si>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamagePerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법으로 만든 화살을 날린다</x:t>
+  </x:si>
+  <x:si>
     <x:t>레벨당 오를 데미지 수치</x:t>
   </x:si>
   <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamagePerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전방으로 불을 뿜는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_MagicArrow</x:t>
   </x:si>
   <x:si>
@@ -148,6 +151,9 @@
   </x:si>
   <x:si>
     <x:t>Anim/AnimController_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDurationPerLevel</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -925,12 +931,12 @@
     <x:col min="10" max="10" width="15.0703125" style="1" bestFit="1" customWidth="1"/>
     <x:col min="11" max="11" width="19.91015625" style="1" bestFit="1" customWidth="1"/>
     <x:col min="12" max="12" width="22.26953125" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="13" max="13" width="24.18359375" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="14" width="24.18359375" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:13" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -938,121 +944,130 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L1" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:13" ht="15.75" customHeight="1">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N1" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="A3" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L3" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="M3" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="K2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="L2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="M2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A3" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L3" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="M3" s="3" t="s">
-        <x:v>14</x:v>
+      <x:c r="N3" s="3" t="s">
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
@@ -1075,22 +1090,22 @@
       <x:c r="M4" s="5">
         <x:v>0.20000000000000001</x:v>
       </x:c>
-      <x:c r="N4" s="4"/>
+      <x:c r="N4" s="5"/>
       <x:c r="O4" s="4"/>
       <x:c r="P4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>0</x:v>
@@ -1105,7 +1120,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J5" s="6">
         <x:v>1.5</x:v>
@@ -1119,22 +1134,22 @@
       <x:c r="M5" s="6">
         <x:v>0.29999999999999999</x:v>
       </x:c>
-      <x:c r="N5" s="4"/>
+      <x:c r="N5" s="6"/>
       <x:c r="O5" s="4"/>
       <x:c r="P5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>0</x:v>
@@ -1159,22 +1174,24 @@
       <x:c r="M6" s="6">
         <x:v>0.20000000000000001</x:v>
       </x:c>
-      <x:c r="N6" s="4"/>
+      <x:c r="N6" s="6">
+        <x:v>0.20000000000000001</x:v>
+      </x:c>
       <x:c r="O6" s="4"/>
       <x:c r="P6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>0</x:v>
@@ -1189,7 +1206,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>
@@ -1199,7 +1216,7 @@
       <x:c r="M7" s="7">
         <x:v>0.20000000000000001</x:v>
       </x:c>
-      <x:c r="N7" s="4"/>
+      <x:c r="N7" s="7"/>
       <x:c r="O7" s="4"/>
       <x:c r="P7" s="4"/>
     </x:row>
@@ -1217,7 +1234,7 @@
       <x:c r="K8" s="7"/>
       <x:c r="L8" s="7"/>
       <x:c r="M8" s="7"/>
-      <x:c r="N8" s="4"/>
+      <x:c r="N8" s="7"/>
       <x:c r="O8" s="4"/>
       <x:c r="P8" s="4"/>
     </x:row>
@@ -1235,7 +1252,7 @@
       <x:c r="K9" s="6"/>
       <x:c r="L9" s="6"/>
       <x:c r="M9" s="6"/>
-      <x:c r="N9" s="4"/>
+      <x:c r="N9" s="6"/>
       <x:c r="O9" s="4"/>
       <x:c r="P9" s="4"/>
     </x:row>
@@ -1253,7 +1270,7 @@
       <x:c r="K10" s="5"/>
       <x:c r="L10" s="5"/>
       <x:c r="M10" s="5"/>
-      <x:c r="N10" s="4"/>
+      <x:c r="N10" s="5"/>
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
     </x:row>
@@ -1271,7 +1288,7 @@
       <x:c r="K11" s="7"/>
       <x:c r="L11" s="7"/>
       <x:c r="M11" s="7"/>
-      <x:c r="N11" s="4"/>
+      <x:c r="N11" s="7"/>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
     </x:row>
@@ -1289,11 +1306,11 @@
       <x:c r="K12" s="7"/>
       <x:c r="L12" s="7"/>
       <x:c r="M12" s="7"/>
-      <x:c r="N12" s="4"/>
+      <x:c r="N12" s="7"/>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
     </x:row>
-    <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
+    <x:row r="13" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A13" s="8"/>
       <x:c r="B13" s="8"/>
       <x:c r="C13" s="8"/>
@@ -1307,8 +1324,9 @@
       <x:c r="K13" s="8"/>
       <x:c r="L13" s="8"/>
       <x:c r="M13" s="8"/>
-    </x:row>
-    <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N13" s="8"/>
+    </x:row>
+    <x:row r="14" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A14" s="9"/>
       <x:c r="B14" s="9"/>
       <x:c r="C14" s="9"/>
@@ -1322,8 +1340,9 @@
       <x:c r="K14" s="8"/>
       <x:c r="L14" s="8"/>
       <x:c r="M14" s="8"/>
-    </x:row>
-    <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N14" s="8"/>
+    </x:row>
+    <x:row r="15" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A15" s="9"/>
       <x:c r="B15" s="9"/>
       <x:c r="C15" s="9"/>
@@ -1337,8 +1356,9 @@
       <x:c r="K15" s="8"/>
       <x:c r="L15" s="8"/>
       <x:c r="M15" s="8"/>
-    </x:row>
-    <x:row r="16" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N15" s="8"/>
+    </x:row>
+    <x:row r="16" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A16" s="9"/>
       <x:c r="B16" s="9"/>
       <x:c r="C16" s="9"/>
@@ -1352,8 +1372,9 @@
       <x:c r="K16" s="8"/>
       <x:c r="L16" s="8"/>
       <x:c r="M16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N16" s="8"/>
+    </x:row>
+    <x:row r="17" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A17" s="9"/>
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="9"/>
@@ -1367,8 +1388,9 @@
       <x:c r="K17" s="8"/>
       <x:c r="L17" s="8"/>
       <x:c r="M17" s="8"/>
-    </x:row>
-    <x:row r="18" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N17" s="8"/>
+    </x:row>
+    <x:row r="18" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A18" s="9"/>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
@@ -1382,8 +1404,9 @@
       <x:c r="K18" s="8"/>
       <x:c r="L18" s="8"/>
       <x:c r="M18" s="8"/>
-    </x:row>
-    <x:row r="19" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
@@ -1397,8 +1420,9 @@
       <x:c r="K19" s="8"/>
       <x:c r="L19" s="8"/>
       <x:c r="M19" s="8"/>
-    </x:row>
-    <x:row r="20" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N19" s="8"/>
+    </x:row>
+    <x:row r="20" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A20" s="9"/>
       <x:c r="B20" s="9"/>
       <x:c r="C20" s="9"/>
@@ -1412,8 +1436,9 @@
       <x:c r="K20" s="8"/>
       <x:c r="L20" s="8"/>
       <x:c r="M20" s="8"/>
-    </x:row>
-    <x:row r="21" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N20" s="8"/>
+    </x:row>
+    <x:row r="21" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A21" s="9"/>
       <x:c r="B21" s="9"/>
       <x:c r="C21" s="9"/>
@@ -1427,8 +1452,9 @@
       <x:c r="K21" s="8"/>
       <x:c r="L21" s="8"/>
       <x:c r="M21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N21" s="8"/>
+    </x:row>
+    <x:row r="22" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A22" s="9"/>
       <x:c r="B22" s="9"/>
       <x:c r="C22" s="9"/>
@@ -1442,8 +1468,9 @@
       <x:c r="K22" s="8"/>
       <x:c r="L22" s="8"/>
       <x:c r="M22" s="8"/>
-    </x:row>
-    <x:row r="23" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N22" s="8"/>
+    </x:row>
+    <x:row r="23" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A23" s="10"/>
       <x:c r="B23" s="10"/>
       <x:c r="C23" s="10"/>
@@ -1457,8 +1484,9 @@
       <x:c r="K23" s="10"/>
       <x:c r="L23" s="10"/>
       <x:c r="M23" s="10"/>
-    </x:row>
-    <x:row r="24" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N23" s="10"/>
+    </x:row>
+    <x:row r="24" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A24" s="10"/>
       <x:c r="B24" s="10"/>
       <x:c r="C24" s="10"/>
@@ -1472,8 +1500,9 @@
       <x:c r="K24" s="10"/>
       <x:c r="L24" s="10"/>
       <x:c r="M24" s="10"/>
-    </x:row>
-    <x:row r="25" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N24" s="10"/>
+    </x:row>
+    <x:row r="25" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A25" s="10"/>
       <x:c r="B25" s="10"/>
       <x:c r="C25" s="10"/>
@@ -1487,8 +1516,9 @@
       <x:c r="K25" s="10"/>
       <x:c r="L25" s="10"/>
       <x:c r="M25" s="10"/>
-    </x:row>
-    <x:row r="26" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N25" s="10"/>
+    </x:row>
+    <x:row r="26" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A26" s="10"/>
       <x:c r="B26" s="10"/>
       <x:c r="C26" s="10"/>
@@ -1502,8 +1532,9 @@
       <x:c r="K26" s="10"/>
       <x:c r="L26" s="10"/>
       <x:c r="M26" s="10"/>
-    </x:row>
-    <x:row r="27" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N26" s="10"/>
+    </x:row>
+    <x:row r="27" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A27" s="10"/>
       <x:c r="B27" s="10"/>
       <x:c r="C27" s="10"/>
@@ -1517,8 +1548,9 @@
       <x:c r="K27" s="10"/>
       <x:c r="L27" s="10"/>
       <x:c r="M27" s="10"/>
-    </x:row>
-    <x:row r="28" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N27" s="10"/>
+    </x:row>
+    <x:row r="28" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A28" s="10"/>
       <x:c r="B28" s="10"/>
       <x:c r="C28" s="10"/>
@@ -1532,8 +1564,9 @@
       <x:c r="K28" s="10"/>
       <x:c r="L28" s="10"/>
       <x:c r="M28" s="10"/>
-    </x:row>
-    <x:row r="29" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N28" s="10"/>
+    </x:row>
+    <x:row r="29" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A29" s="11"/>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="11"/>
@@ -1547,8 +1580,9 @@
       <x:c r="K29" s="11"/>
       <x:c r="L29" s="11"/>
       <x:c r="M29" s="11"/>
-    </x:row>
-    <x:row r="30" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N29" s="11"/>
+    </x:row>
+    <x:row r="30" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A30" s="11"/>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="11"/>
@@ -1562,8 +1596,9 @@
       <x:c r="K30" s="11"/>
       <x:c r="L30" s="11"/>
       <x:c r="M30" s="11"/>
-    </x:row>
-    <x:row r="31" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N30" s="11"/>
+    </x:row>
+    <x:row r="31" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A31" s="11"/>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="11"/>
@@ -1577,8 +1612,9 @@
       <x:c r="K31" s="11"/>
       <x:c r="L31" s="11"/>
       <x:c r="M31" s="11"/>
-    </x:row>
-    <x:row r="32" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="N31" s="11"/>
+    </x:row>
+    <x:row r="32" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A32" s="11"/>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="11"/>
@@ -1592,6 +1628,7 @@
       <x:c r="K32" s="11"/>
       <x:c r="L32" s="11"/>
       <x:c r="M32" s="11"/>
+      <x:c r="N32" s="11"/>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1"/>
     <x:row r="34" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -21,133 +21,133 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamagePerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 데미지 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolDownPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
     <x:t>스킬 지속시간</x:t>
   </x:si>
   <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolDownPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법으로 만든 화살을 날린다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다 (스킬 레벨이 증가할수록 얼어있는 시간이 늘어난다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가까운 적에게 번개를 쏜다 (스킬 레벨이 증가할수록 번개 줄기가 늘어난다)</x:t>
   </x:si>
   <x:si>
     <x:t>Anim/AnimController_Lightning</x:t>
   </x:si>
   <x:si>
-    <x:t>가까운 적에게 번개를 쏜다(혹은 하늘에서 번개를 떨군다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전방으로 불을 뿜는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 오를 스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamagePerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 오를 데미지 수치</x:t>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
   </x:si>
   <x:si>
     <x:t>Anim/AnimController_Fire</x:t>
@@ -921,7 +921,7 @@
   <x:cols>
     <x:col min="1" max="1" width="23" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="50.7109375" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="82.5703125" style="1" bestFit="1" customWidth="1"/>
     <x:col min="4" max="4" width="26.09765625" style="1" bestFit="1" customWidth="1"/>
     <x:col min="5" max="5" width="10.34375" style="1" bestFit="1" customWidth="1"/>
     <x:col min="6" max="6" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -936,7 +936,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -944,113 +944,113 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L1" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N1" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="M2" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="N2" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="L3" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M3" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="N3" s="3" t="s">
         <x:v>44</x:v>
@@ -1058,16 +1058,16 @@
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
@@ -1096,22 +1096,22 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="s">
+      <x:c r="D5" s="6" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="6">
-        <x:v>200</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G5" s="6">
         <x:v>8</x:v>
@@ -1126,10 +1126,10 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K5" s="6">
-        <x:v>1.2</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="L5" s="5">
-        <x:v>200</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M5" s="6">
         <x:v>0.29999999999999999</x:v>
@@ -1140,16 +1140,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>9</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>0</x:v>
@@ -1182,16 +1182,16 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>0</x:v>
@@ -1206,7 +1206,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -21,129 +21,132 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <x:si>
+    <x:t>마법으로 만든 화살을 날린다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamagePerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 데미지 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
     <x:t>SkillDistance</x:t>
   </x:si>
   <x:si>
-    <x:t>SkillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DamagePerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 오를 데미지 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 오를 스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
+    <x:t>SkillDurationPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolDownPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다 (스킬 레벨이 증가할수록 얼어있는 시간이 늘어난다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전방으로 불을 뿜는다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가까운 적에게 번개를 쏜다 (스킬 레벨이 증가할수록 번개 줄기가 늘어난다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolDownPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전방으로 불을 뿜는다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다 (스킬 레벨이 증가할수록 얼어있는 시간이 늘어난다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다 (스킬 레벨이 증가할수록 번개 줄기가 늘어난다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Lightning</x:t>
   </x:si>
   <x:si>
@@ -151,9 +154,6 @@
   </x:si>
   <x:si>
     <x:t>Anim/AnimController_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDurationPerLevel</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -936,7 +936,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -944,101 +944,101 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L1" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N1" s="2" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="N1" s="2" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H3" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J3" s="3" t="s">
         <x:v>4</x:v>
@@ -1047,33 +1047,33 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L3" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M3" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N3" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E4" s="5">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="5">
-        <x:v>120</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G4" s="5">
         <x:v>10</x:v>
@@ -1085,7 +1085,7 @@
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5">
-        <x:v>120</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="M4" s="5">
         <x:v>0.20000000000000001</x:v>
@@ -1099,19 +1099,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="6">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G5" s="6">
         <x:v>8</x:v>
@@ -1120,7 +1120,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J5" s="6">
         <x:v>1.5</x:v>
@@ -1140,16 +1140,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>0</x:v>
@@ -1182,22 +1182,22 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="7">
-        <x:v>150</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G7" s="7">
         <x:v>8</x:v>
@@ -1206,7 +1206,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="16332" windowHeight="6744"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,139 +21,139 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <x:si>
+    <x:t>전방으로 불을 뿜는다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다 (스킬 레벨이 증가할수록 얼어있는 시간이 늘어난다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolDownPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamagePerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 데미지 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
     <x:t>마법으로 만든 화살을 날린다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
   </x:si>
   <x:si>
-    <x:t>DamagePerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 오를 데미지 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 오를 스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDistance</x:t>
+    <x:t>가까운 적에게 번개를 쏜다 (스킬 레벨이 증가할수록 번개 줄기가 늘어난다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Fire</x:t>
   </x:si>
   <x:si>
     <x:t>SkillDurationPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolDownPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다 (스킬 레벨이 증가할수록 얼어있는 시간이 늘어난다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전방으로 불을 뿜는다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다 (스킬 레벨이 증가할수록 번개 줄기가 늘어난다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Fire</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -936,7 +936,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -944,133 +944,133 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="N1" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="N2" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L3" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="L3" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="M3" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="N3" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E4" s="5">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="5">
         <x:v>150</x:v>
@@ -1096,16 +1096,16 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="6">
         <x:v>0</x:v>
@@ -1120,7 +1120,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J5" s="6">
         <x:v>1.5</x:v>
@@ -1140,16 +1140,16 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>26</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E6" s="6">
         <x:v>0</x:v>
@@ -1182,16 +1182,16 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="7">
         <x:v>0</x:v>
@@ -1206,7 +1206,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="7"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="16332" windowHeight="6744"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,24 +19,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
+  <x:si>
+    <x:t>마법으로 만든 화살을 날린다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각성스킬 데미지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬범위 안의 적들을 얼린다 (스킬 레벨이 증가할수록 얼어있는 시간이 늘어난다)</x:t>
+  </x:si>
   <x:si>
     <x:t>전방으로 불을 뿜는다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬범위 안의 적들을 얼린다 (스킬 레벨이 증가할수록 얼어있는 시간이 늘어난다)</x:t>
+    <x:t>AwakedDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가까운 적에게 번개를 쏜다 (스킬 레벨이 증가할수록 번개 줄기가 늘어난다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolDownPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
+    <x:t>스킬 지속시간</x:t>
   </x:si>
   <x:si>
     <x:t>라이트닝</x:t>
@@ -45,115 +123,49 @@
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolDownPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
+    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamagePerLevel</x:t>
   </x:si>
   <x:si>
     <x:t>SkillCoolTime</x:t>
   </x:si>
   <x:si>
-    <x:t>DamagePerLevel</x:t>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
   </x:si>
   <x:si>
     <x:t>레벨당 오를 데미지 수치</x:t>
   </x:si>
   <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 줄어들 쿨타임 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fire_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>SkillDistance</x:t>
   </x:si>
   <x:si>
-    <x:t>레벨당 오를 스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법으로 만든 화살을 날린다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가까운 적에게 번개를 쏜다 (스킬 레벨이 증가할수록 번개 줄기가 늘어난다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사거리</x:t>
+    <x:t>Anim/AnimController_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Lightning</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Fire</x:t>
-  </x:si>
-  <x:si>
     <x:t>SkillDurationPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AwakedCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각성스킬 쿨타임</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -275,7 +287,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -287,9 +299,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
@@ -931,12 +940,12 @@
     <x:col min="10" max="10" width="15.0703125" style="1" bestFit="1" customWidth="1"/>
     <x:col min="11" max="11" width="19.91015625" style="1" bestFit="1" customWidth="1"/>
     <x:col min="12" max="12" width="22.26953125" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="13" max="14" width="24.18359375" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="16" width="24.18359375" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -944,299 +953,333 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M1" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="N1" s="2" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="O1" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="P1" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A2" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="M2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="O2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="P2" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A3" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L3" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="M3" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N3" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O3" s="3" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="P3" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A4" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E4" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="4">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G4" s="4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H4" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I4" s="4"/>
+      <x:c r="J4" s="4"/>
+      <x:c r="K4" s="4"/>
+      <x:c r="L4" s="4">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="M4" s="4">
+        <x:v>0.20000000000000001</x:v>
+      </x:c>
+      <x:c r="N4" s="4"/>
+      <x:c r="O4" s="4">
+        <x:v>0.10000000000000001</x:v>
+      </x:c>
+      <x:c r="P4" s="4">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A5" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E5" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="5">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G5" s="5">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H5" s="5">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I5" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J5" s="5">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="K5" s="5">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L5" s="4">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M5" s="5">
+        <x:v>0.29999999999999999</x:v>
+      </x:c>
+      <x:c r="N5" s="5"/>
+      <x:c r="O5" s="5">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P5" s="5">
+        <x:v>3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A6" s="5" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="B6" s="5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="5">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="5">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G6" s="5">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H6" s="5">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="I6" s="4"/>
+      <x:c r="J6" s="5">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K6" s="5"/>
+      <x:c r="L6" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="M6" s="5">
+        <x:v>0.20000000000000001</x:v>
+      </x:c>
+      <x:c r="N6" s="5">
+        <x:v>0.20000000000000001</x:v>
+      </x:c>
+      <x:c r="O6" s="5">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P6" s="5">
+        <x:v>4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A7" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E7" s="6">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="6">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G7" s="6">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H7" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I7" s="4" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="N1" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A2" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
+      <x:c r="J7" s="6"/>
+      <x:c r="K7" s="6"/>
+      <x:c r="L7" s="4">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M7" s="6">
+        <x:v>0.20000000000000001</x:v>
+      </x:c>
+      <x:c r="N7" s="6"/>
+      <x:c r="O7" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="L2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="M2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="N2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A3" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L3" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="M3" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="N3" s="3" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A4" s="5" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E4" s="5">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="5">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G4" s="5">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H4" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I4" s="5"/>
-      <x:c r="J4" s="5"/>
-      <x:c r="K4" s="5"/>
-      <x:c r="L4" s="5">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="M4" s="5">
-        <x:v>0.20000000000000001</x:v>
-      </x:c>
-      <x:c r="N4" s="5"/>
-      <x:c r="O4" s="4"/>
-      <x:c r="P4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A5" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E5" s="6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F5" s="6">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G5" s="6">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H5" s="6">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I5" s="5" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J5" s="6">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="K5" s="6">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="L5" s="5">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M5" s="6">
-        <x:v>0.29999999999999999</x:v>
-      </x:c>
-      <x:c r="N5" s="6"/>
-      <x:c r="O5" s="4"/>
-      <x:c r="P5" s="4"/>
-    </x:row>
-    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A6" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="6">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G6" s="6">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H6" s="6">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I6" s="5"/>
-      <x:c r="J6" s="6">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K6" s="6"/>
-      <x:c r="L6" s="5">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="M6" s="6">
-        <x:v>0.20000000000000001</x:v>
-      </x:c>
-      <x:c r="N6" s="6">
-        <x:v>0.20000000000000001</x:v>
-      </x:c>
-      <x:c r="O6" s="4"/>
-      <x:c r="P6" s="4"/>
-    </x:row>
-    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A7" s="6" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D7" s="7" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E7" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="7">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G7" s="7">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H7" s="7">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I7" s="5" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="J7" s="7"/>
-      <x:c r="K7" s="7"/>
-      <x:c r="L7" s="5">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M7" s="7">
-        <x:v>0.20000000000000001</x:v>
-      </x:c>
-      <x:c r="N7" s="7"/>
-      <x:c r="O7" s="4"/>
-      <x:c r="P7" s="4"/>
+      <x:c r="P7" s="6">
+        <x:v>5000</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A8" s="7"/>
-      <x:c r="B8" s="7"/>
-      <x:c r="C8" s="7"/>
-      <x:c r="D8" s="7"/>
-      <x:c r="E8" s="7"/>
-      <x:c r="F8" s="7"/>
-      <x:c r="G8" s="7"/>
-      <x:c r="H8" s="7"/>
-      <x:c r="I8" s="7"/>
-      <x:c r="J8" s="7"/>
-      <x:c r="K8" s="7"/>
-      <x:c r="L8" s="7"/>
-      <x:c r="M8" s="7"/>
-      <x:c r="N8" s="7"/>
-      <x:c r="O8" s="4"/>
-      <x:c r="P8" s="4"/>
+      <x:c r="A8" s="6"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6"/>
+      <x:c r="F8" s="6"/>
+      <x:c r="G8" s="6"/>
+      <x:c r="H8" s="6"/>
+      <x:c r="I8" s="6"/>
+      <x:c r="J8" s="6"/>
+      <x:c r="K8" s="6"/>
+      <x:c r="L8" s="6"/>
+      <x:c r="M8" s="6"/>
+      <x:c r="N8" s="6"/>
+      <x:c r="O8" s="6"/>
+      <x:c r="P8" s="6"/>
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="6"/>
@@ -1253,382 +1296,422 @@
       <x:c r="L9" s="6"/>
       <x:c r="M9" s="6"/>
       <x:c r="N9" s="6"/>
-      <x:c r="O9" s="4"/>
-      <x:c r="P9" s="4"/>
+      <x:c r="O9" s="6"/>
+      <x:c r="P9" s="6"/>
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A10" s="5"/>
-      <x:c r="B10" s="5"/>
-      <x:c r="C10" s="5"/>
-      <x:c r="D10" s="5"/>
-      <x:c r="E10" s="5"/>
-      <x:c r="F10" s="5"/>
-      <x:c r="G10" s="5"/>
-      <x:c r="H10" s="5"/>
-      <x:c r="I10" s="5"/>
-      <x:c r="J10" s="5"/>
-      <x:c r="K10" s="5"/>
-      <x:c r="L10" s="5"/>
-      <x:c r="M10" s="5"/>
-      <x:c r="N10" s="5"/>
+      <x:c r="A10" s="4"/>
+      <x:c r="B10" s="4"/>
+      <x:c r="C10" s="4"/>
+      <x:c r="D10" s="4"/>
+      <x:c r="E10" s="4"/>
+      <x:c r="F10" s="4"/>
+      <x:c r="G10" s="4"/>
+      <x:c r="H10" s="4"/>
+      <x:c r="I10" s="4"/>
+      <x:c r="J10" s="4"/>
+      <x:c r="K10" s="4"/>
+      <x:c r="L10" s="4"/>
+      <x:c r="M10" s="4"/>
+      <x:c r="N10" s="4"/>
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A11" s="7"/>
-      <x:c r="B11" s="7"/>
-      <x:c r="C11" s="7"/>
-      <x:c r="D11" s="7"/>
-      <x:c r="E11" s="7"/>
-      <x:c r="F11" s="7"/>
-      <x:c r="G11" s="7"/>
-      <x:c r="H11" s="7"/>
-      <x:c r="I11" s="7"/>
-      <x:c r="J11" s="7"/>
-      <x:c r="K11" s="7"/>
-      <x:c r="L11" s="7"/>
-      <x:c r="M11" s="7"/>
-      <x:c r="N11" s="7"/>
-      <x:c r="O11" s="4"/>
-      <x:c r="P11" s="4"/>
+      <x:c r="A11" s="6"/>
+      <x:c r="B11" s="6"/>
+      <x:c r="C11" s="6"/>
+      <x:c r="D11" s="6"/>
+      <x:c r="E11" s="6"/>
+      <x:c r="F11" s="6"/>
+      <x:c r="G11" s="6"/>
+      <x:c r="H11" s="6"/>
+      <x:c r="I11" s="6"/>
+      <x:c r="J11" s="6"/>
+      <x:c r="K11" s="6"/>
+      <x:c r="L11" s="6"/>
+      <x:c r="M11" s="6"/>
+      <x:c r="N11" s="6"/>
+      <x:c r="O11" s="6"/>
+      <x:c r="P11" s="6"/>
     </x:row>
     <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A12" s="7"/>
-      <x:c r="B12" s="7"/>
-      <x:c r="C12" s="7"/>
-      <x:c r="D12" s="7"/>
-      <x:c r="E12" s="7"/>
-      <x:c r="F12" s="7"/>
-      <x:c r="G12" s="7"/>
-      <x:c r="H12" s="7"/>
-      <x:c r="I12" s="7"/>
-      <x:c r="J12" s="7"/>
-      <x:c r="K12" s="7"/>
-      <x:c r="L12" s="7"/>
-      <x:c r="M12" s="7"/>
-      <x:c r="N12" s="7"/>
-      <x:c r="O12" s="4"/>
-      <x:c r="P12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A13" s="8"/>
-      <x:c r="B13" s="8"/>
-      <x:c r="C13" s="8"/>
-      <x:c r="D13" s="8"/>
-      <x:c r="E13" s="8"/>
-      <x:c r="F13" s="8"/>
-      <x:c r="G13" s="8"/>
-      <x:c r="H13" s="8"/>
-      <x:c r="I13" s="8"/>
-      <x:c r="J13" s="8"/>
-      <x:c r="K13" s="8"/>
-      <x:c r="L13" s="8"/>
-      <x:c r="M13" s="8"/>
-      <x:c r="N13" s="8"/>
-    </x:row>
-    <x:row r="14" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A14" s="9"/>
-      <x:c r="B14" s="9"/>
-      <x:c r="C14" s="9"/>
-      <x:c r="D14" s="8"/>
-      <x:c r="E14" s="8"/>
-      <x:c r="F14" s="8"/>
-      <x:c r="G14" s="8"/>
-      <x:c r="H14" s="8"/>
-      <x:c r="I14" s="8"/>
-      <x:c r="J14" s="8"/>
-      <x:c r="K14" s="8"/>
-      <x:c r="L14" s="8"/>
-      <x:c r="M14" s="8"/>
-      <x:c r="N14" s="8"/>
-    </x:row>
-    <x:row r="15" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A15" s="9"/>
-      <x:c r="B15" s="9"/>
-      <x:c r="C15" s="9"/>
-      <x:c r="D15" s="8"/>
-      <x:c r="E15" s="8"/>
-      <x:c r="F15" s="8"/>
-      <x:c r="G15" s="8"/>
-      <x:c r="H15" s="8"/>
-      <x:c r="I15" s="8"/>
-      <x:c r="J15" s="8"/>
-      <x:c r="K15" s="8"/>
-      <x:c r="L15" s="8"/>
-      <x:c r="M15" s="8"/>
-      <x:c r="N15" s="8"/>
-    </x:row>
-    <x:row r="16" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A16" s="9"/>
-      <x:c r="B16" s="9"/>
-      <x:c r="C16" s="9"/>
-      <x:c r="D16" s="8"/>
-      <x:c r="E16" s="8"/>
-      <x:c r="F16" s="8"/>
-      <x:c r="G16" s="8"/>
-      <x:c r="H16" s="8"/>
-      <x:c r="I16" s="8"/>
-      <x:c r="J16" s="8"/>
-      <x:c r="K16" s="8"/>
-      <x:c r="L16" s="8"/>
-      <x:c r="M16" s="8"/>
-      <x:c r="N16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A17" s="9"/>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-      <x:c r="D17" s="8"/>
-      <x:c r="E17" s="8"/>
-      <x:c r="F17" s="8"/>
-      <x:c r="G17" s="8"/>
-      <x:c r="H17" s="8"/>
-      <x:c r="I17" s="8"/>
-      <x:c r="J17" s="8"/>
-      <x:c r="K17" s="8"/>
-      <x:c r="L17" s="8"/>
-      <x:c r="M17" s="8"/>
-      <x:c r="N17" s="8"/>
-    </x:row>
-    <x:row r="18" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A18" s="9"/>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="8"/>
-      <x:c r="E18" s="8"/>
-      <x:c r="F18" s="8"/>
-      <x:c r="G18" s="8"/>
-      <x:c r="H18" s="8"/>
-      <x:c r="I18" s="8"/>
-      <x:c r="J18" s="8"/>
-      <x:c r="K18" s="8"/>
-      <x:c r="L18" s="8"/>
-      <x:c r="M18" s="8"/>
-      <x:c r="N18" s="8"/>
-    </x:row>
-    <x:row r="19" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A19" s="9"/>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="8"/>
-      <x:c r="E19" s="8"/>
-      <x:c r="F19" s="8"/>
-      <x:c r="G19" s="8"/>
-      <x:c r="H19" s="8"/>
-      <x:c r="I19" s="8"/>
-      <x:c r="J19" s="8"/>
-      <x:c r="K19" s="8"/>
-      <x:c r="L19" s="8"/>
-      <x:c r="M19" s="8"/>
-      <x:c r="N19" s="8"/>
-    </x:row>
-    <x:row r="20" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A20" s="9"/>
-      <x:c r="B20" s="9"/>
-      <x:c r="C20" s="9"/>
-      <x:c r="D20" s="8"/>
-      <x:c r="E20" s="8"/>
-      <x:c r="F20" s="8"/>
-      <x:c r="G20" s="8"/>
-      <x:c r="H20" s="8"/>
-      <x:c r="I20" s="8"/>
-      <x:c r="J20" s="8"/>
-      <x:c r="K20" s="8"/>
-      <x:c r="L20" s="8"/>
-      <x:c r="M20" s="8"/>
-      <x:c r="N20" s="8"/>
-    </x:row>
-    <x:row r="21" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A21" s="9"/>
-      <x:c r="B21" s="9"/>
-      <x:c r="C21" s="9"/>
-      <x:c r="D21" s="8"/>
-      <x:c r="E21" s="8"/>
-      <x:c r="F21" s="8"/>
-      <x:c r="G21" s="8"/>
-      <x:c r="H21" s="8"/>
-      <x:c r="I21" s="8"/>
-      <x:c r="J21" s="8"/>
-      <x:c r="K21" s="8"/>
-      <x:c r="L21" s="8"/>
-      <x:c r="M21" s="8"/>
-      <x:c r="N21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A22" s="9"/>
-      <x:c r="B22" s="9"/>
-      <x:c r="C22" s="9"/>
-      <x:c r="D22" s="8"/>
-      <x:c r="E22" s="8"/>
-      <x:c r="F22" s="8"/>
-      <x:c r="G22" s="8"/>
-      <x:c r="H22" s="8"/>
-      <x:c r="I22" s="8"/>
-      <x:c r="J22" s="8"/>
-      <x:c r="K22" s="8"/>
-      <x:c r="L22" s="8"/>
-      <x:c r="M22" s="8"/>
-      <x:c r="N22" s="8"/>
-    </x:row>
-    <x:row r="23" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A23" s="10"/>
-      <x:c r="B23" s="10"/>
-      <x:c r="C23" s="10"/>
-      <x:c r="D23" s="10"/>
-      <x:c r="E23" s="10"/>
-      <x:c r="F23" s="10"/>
-      <x:c r="G23" s="10"/>
-      <x:c r="H23" s="10"/>
-      <x:c r="I23" s="10"/>
-      <x:c r="J23" s="10"/>
-      <x:c r="K23" s="10"/>
-      <x:c r="L23" s="10"/>
-      <x:c r="M23" s="10"/>
-      <x:c r="N23" s="10"/>
-    </x:row>
-    <x:row r="24" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A24" s="10"/>
-      <x:c r="B24" s="10"/>
-      <x:c r="C24" s="10"/>
-      <x:c r="D24" s="10"/>
-      <x:c r="E24" s="10"/>
-      <x:c r="F24" s="10"/>
-      <x:c r="G24" s="10"/>
-      <x:c r="H24" s="10"/>
-      <x:c r="I24" s="10"/>
-      <x:c r="J24" s="10"/>
-      <x:c r="K24" s="10"/>
-      <x:c r="L24" s="10"/>
-      <x:c r="M24" s="10"/>
-      <x:c r="N24" s="10"/>
-    </x:row>
-    <x:row r="25" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A25" s="10"/>
-      <x:c r="B25" s="10"/>
-      <x:c r="C25" s="10"/>
-      <x:c r="D25" s="10"/>
-      <x:c r="E25" s="10"/>
-      <x:c r="F25" s="10"/>
-      <x:c r="G25" s="10"/>
-      <x:c r="H25" s="10"/>
-      <x:c r="I25" s="10"/>
-      <x:c r="J25" s="10"/>
-      <x:c r="K25" s="10"/>
-      <x:c r="L25" s="10"/>
-      <x:c r="M25" s="10"/>
-      <x:c r="N25" s="10"/>
-    </x:row>
-    <x:row r="26" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A26" s="10"/>
-      <x:c r="B26" s="10"/>
-      <x:c r="C26" s="10"/>
-      <x:c r="D26" s="10"/>
-      <x:c r="E26" s="10"/>
-      <x:c r="F26" s="10"/>
-      <x:c r="G26" s="10"/>
-      <x:c r="H26" s="10"/>
-      <x:c r="I26" s="10"/>
-      <x:c r="J26" s="10"/>
-      <x:c r="K26" s="10"/>
-      <x:c r="L26" s="10"/>
-      <x:c r="M26" s="10"/>
-      <x:c r="N26" s="10"/>
-    </x:row>
-    <x:row r="27" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A27" s="10"/>
-      <x:c r="B27" s="10"/>
-      <x:c r="C27" s="10"/>
-      <x:c r="D27" s="10"/>
-      <x:c r="E27" s="10"/>
-      <x:c r="F27" s="10"/>
-      <x:c r="G27" s="10"/>
-      <x:c r="H27" s="10"/>
-      <x:c r="I27" s="10"/>
-      <x:c r="J27" s="10"/>
-      <x:c r="K27" s="10"/>
-      <x:c r="L27" s="10"/>
-      <x:c r="M27" s="10"/>
-      <x:c r="N27" s="10"/>
-    </x:row>
-    <x:row r="28" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A28" s="10"/>
-      <x:c r="B28" s="10"/>
-      <x:c r="C28" s="10"/>
-      <x:c r="D28" s="10"/>
-      <x:c r="E28" s="10"/>
-      <x:c r="F28" s="10"/>
-      <x:c r="G28" s="10"/>
-      <x:c r="H28" s="10"/>
-      <x:c r="I28" s="10"/>
-      <x:c r="J28" s="10"/>
-      <x:c r="K28" s="10"/>
-      <x:c r="L28" s="10"/>
-      <x:c r="M28" s="10"/>
-      <x:c r="N28" s="10"/>
-    </x:row>
-    <x:row r="29" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A29" s="11"/>
-      <x:c r="B29" s="11"/>
-      <x:c r="C29" s="11"/>
-      <x:c r="D29" s="11"/>
-      <x:c r="E29" s="11"/>
-      <x:c r="F29" s="11"/>
-      <x:c r="G29" s="11"/>
-      <x:c r="H29" s="11"/>
-      <x:c r="I29" s="11"/>
-      <x:c r="J29" s="11"/>
-      <x:c r="K29" s="11"/>
-      <x:c r="L29" s="11"/>
-      <x:c r="M29" s="11"/>
-      <x:c r="N29" s="11"/>
-    </x:row>
-    <x:row r="30" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A30" s="11"/>
-      <x:c r="B30" s="11"/>
-      <x:c r="C30" s="11"/>
-      <x:c r="D30" s="11"/>
-      <x:c r="E30" s="11"/>
-      <x:c r="F30" s="11"/>
-      <x:c r="G30" s="11"/>
-      <x:c r="H30" s="11"/>
-      <x:c r="I30" s="11"/>
-      <x:c r="J30" s="11"/>
-      <x:c r="K30" s="11"/>
-      <x:c r="L30" s="11"/>
-      <x:c r="M30" s="11"/>
-      <x:c r="N30" s="11"/>
-    </x:row>
-    <x:row r="31" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A31" s="11"/>
-      <x:c r="B31" s="11"/>
-      <x:c r="C31" s="11"/>
-      <x:c r="D31" s="11"/>
-      <x:c r="E31" s="11"/>
-      <x:c r="F31" s="11"/>
-      <x:c r="G31" s="11"/>
-      <x:c r="H31" s="11"/>
-      <x:c r="I31" s="11"/>
-      <x:c r="J31" s="11"/>
-      <x:c r="K31" s="11"/>
-      <x:c r="L31" s="11"/>
-      <x:c r="M31" s="11"/>
-      <x:c r="N31" s="11"/>
-    </x:row>
-    <x:row r="32" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A32" s="11"/>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="11"/>
-      <x:c r="D32" s="11"/>
-      <x:c r="E32" s="11"/>
-      <x:c r="F32" s="11"/>
-      <x:c r="G32" s="11"/>
-      <x:c r="H32" s="11"/>
-      <x:c r="I32" s="11"/>
-      <x:c r="J32" s="11"/>
-      <x:c r="K32" s="11"/>
-      <x:c r="L32" s="11"/>
-      <x:c r="M32" s="11"/>
-      <x:c r="N32" s="11"/>
+      <x:c r="A12" s="6"/>
+      <x:c r="B12" s="6"/>
+      <x:c r="C12" s="6"/>
+      <x:c r="D12" s="6"/>
+      <x:c r="E12" s="6"/>
+      <x:c r="F12" s="6"/>
+      <x:c r="G12" s="6"/>
+      <x:c r="H12" s="6"/>
+      <x:c r="I12" s="6"/>
+      <x:c r="J12" s="6"/>
+      <x:c r="K12" s="6"/>
+      <x:c r="L12" s="6"/>
+      <x:c r="M12" s="6"/>
+      <x:c r="N12" s="6"/>
+      <x:c r="O12" s="6"/>
+      <x:c r="P12" s="6"/>
+    </x:row>
+    <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A13" s="7"/>
+      <x:c r="B13" s="7"/>
+      <x:c r="C13" s="7"/>
+      <x:c r="D13" s="7"/>
+      <x:c r="E13" s="7"/>
+      <x:c r="F13" s="7"/>
+      <x:c r="G13" s="7"/>
+      <x:c r="H13" s="7"/>
+      <x:c r="I13" s="7"/>
+      <x:c r="J13" s="7"/>
+      <x:c r="K13" s="7"/>
+      <x:c r="L13" s="7"/>
+      <x:c r="M13" s="7"/>
+      <x:c r="N13" s="7"/>
+      <x:c r="O13" s="7"/>
+      <x:c r="P13" s="7"/>
+    </x:row>
+    <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A14" s="8"/>
+      <x:c r="B14" s="8"/>
+      <x:c r="C14" s="8"/>
+      <x:c r="D14" s="7"/>
+      <x:c r="E14" s="7"/>
+      <x:c r="F14" s="7"/>
+      <x:c r="G14" s="7"/>
+      <x:c r="H14" s="7"/>
+      <x:c r="I14" s="7"/>
+      <x:c r="J14" s="7"/>
+      <x:c r="K14" s="7"/>
+      <x:c r="L14" s="7"/>
+      <x:c r="M14" s="7"/>
+      <x:c r="N14" s="7"/>
+      <x:c r="O14" s="7"/>
+      <x:c r="P14" s="7"/>
+    </x:row>
+    <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A15" s="8"/>
+      <x:c r="B15" s="8"/>
+      <x:c r="C15" s="8"/>
+      <x:c r="D15" s="7"/>
+      <x:c r="E15" s="7"/>
+      <x:c r="F15" s="7"/>
+      <x:c r="G15" s="7"/>
+      <x:c r="H15" s="7"/>
+      <x:c r="I15" s="7"/>
+      <x:c r="J15" s="7"/>
+      <x:c r="K15" s="7"/>
+      <x:c r="L15" s="7"/>
+      <x:c r="M15" s="7"/>
+      <x:c r="N15" s="7"/>
+      <x:c r="O15" s="7"/>
+      <x:c r="P15" s="7"/>
+    </x:row>
+    <x:row r="16" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A16" s="8"/>
+      <x:c r="B16" s="8"/>
+      <x:c r="C16" s="8"/>
+      <x:c r="D16" s="7"/>
+      <x:c r="E16" s="7"/>
+      <x:c r="F16" s="7"/>
+      <x:c r="G16" s="7"/>
+      <x:c r="H16" s="7"/>
+      <x:c r="I16" s="7"/>
+      <x:c r="J16" s="7"/>
+      <x:c r="K16" s="7"/>
+      <x:c r="L16" s="7"/>
+      <x:c r="M16" s="7"/>
+      <x:c r="N16" s="7"/>
+      <x:c r="O16" s="7"/>
+      <x:c r="P16" s="7"/>
+    </x:row>
+    <x:row r="17" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A17" s="8"/>
+      <x:c r="B17" s="8"/>
+      <x:c r="C17" s="8"/>
+      <x:c r="D17" s="7"/>
+      <x:c r="E17" s="7"/>
+      <x:c r="F17" s="7"/>
+      <x:c r="G17" s="7"/>
+      <x:c r="H17" s="7"/>
+      <x:c r="I17" s="7"/>
+      <x:c r="J17" s="7"/>
+      <x:c r="K17" s="7"/>
+      <x:c r="L17" s="7"/>
+      <x:c r="M17" s="7"/>
+      <x:c r="N17" s="7"/>
+      <x:c r="O17" s="7"/>
+      <x:c r="P17" s="7"/>
+    </x:row>
+    <x:row r="18" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A18" s="8"/>
+      <x:c r="B18" s="8"/>
+      <x:c r="C18" s="8"/>
+      <x:c r="D18" s="7"/>
+      <x:c r="E18" s="7"/>
+      <x:c r="F18" s="7"/>
+      <x:c r="G18" s="7"/>
+      <x:c r="H18" s="7"/>
+      <x:c r="I18" s="7"/>
+      <x:c r="J18" s="7"/>
+      <x:c r="K18" s="7"/>
+      <x:c r="L18" s="7"/>
+      <x:c r="M18" s="7"/>
+      <x:c r="N18" s="7"/>
+      <x:c r="O18" s="7"/>
+      <x:c r="P18" s="7"/>
+    </x:row>
+    <x:row r="19" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A19" s="8"/>
+      <x:c r="B19" s="8"/>
+      <x:c r="C19" s="8"/>
+      <x:c r="D19" s="7"/>
+      <x:c r="E19" s="7"/>
+      <x:c r="F19" s="7"/>
+      <x:c r="G19" s="7"/>
+      <x:c r="H19" s="7"/>
+      <x:c r="I19" s="7"/>
+      <x:c r="J19" s="7"/>
+      <x:c r="K19" s="7"/>
+      <x:c r="L19" s="7"/>
+      <x:c r="M19" s="7"/>
+      <x:c r="N19" s="7"/>
+      <x:c r="O19" s="7"/>
+      <x:c r="P19" s="7"/>
+    </x:row>
+    <x:row r="20" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A20" s="8"/>
+      <x:c r="B20" s="8"/>
+      <x:c r="C20" s="8"/>
+      <x:c r="D20" s="7"/>
+      <x:c r="E20" s="7"/>
+      <x:c r="F20" s="7"/>
+      <x:c r="G20" s="7"/>
+      <x:c r="H20" s="7"/>
+      <x:c r="I20" s="7"/>
+      <x:c r="J20" s="7"/>
+      <x:c r="K20" s="7"/>
+      <x:c r="L20" s="7"/>
+      <x:c r="M20" s="7"/>
+      <x:c r="N20" s="7"/>
+      <x:c r="O20" s="7"/>
+      <x:c r="P20" s="7"/>
+    </x:row>
+    <x:row r="21" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A21" s="8"/>
+      <x:c r="B21" s="8"/>
+      <x:c r="C21" s="8"/>
+      <x:c r="D21" s="7"/>
+      <x:c r="E21" s="7"/>
+      <x:c r="F21" s="7"/>
+      <x:c r="G21" s="7"/>
+      <x:c r="H21" s="7"/>
+      <x:c r="I21" s="7"/>
+      <x:c r="J21" s="7"/>
+      <x:c r="K21" s="7"/>
+      <x:c r="L21" s="7"/>
+      <x:c r="M21" s="7"/>
+      <x:c r="N21" s="7"/>
+      <x:c r="O21" s="7"/>
+      <x:c r="P21" s="7"/>
+    </x:row>
+    <x:row r="22" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A22" s="8"/>
+      <x:c r="B22" s="8"/>
+      <x:c r="C22" s="8"/>
+      <x:c r="D22" s="7"/>
+      <x:c r="E22" s="7"/>
+      <x:c r="F22" s="7"/>
+      <x:c r="G22" s="7"/>
+      <x:c r="H22" s="7"/>
+      <x:c r="I22" s="7"/>
+      <x:c r="J22" s="7"/>
+      <x:c r="K22" s="7"/>
+      <x:c r="L22" s="7"/>
+      <x:c r="M22" s="7"/>
+      <x:c r="N22" s="7"/>
+      <x:c r="O22" s="7"/>
+      <x:c r="P22" s="7"/>
+    </x:row>
+    <x:row r="23" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A23" s="9"/>
+      <x:c r="B23" s="9"/>
+      <x:c r="C23" s="9"/>
+      <x:c r="D23" s="9"/>
+      <x:c r="E23" s="9"/>
+      <x:c r="F23" s="9"/>
+      <x:c r="G23" s="9"/>
+      <x:c r="H23" s="9"/>
+      <x:c r="I23" s="9"/>
+      <x:c r="J23" s="9"/>
+      <x:c r="K23" s="9"/>
+      <x:c r="L23" s="9"/>
+      <x:c r="M23" s="9"/>
+      <x:c r="N23" s="9"/>
+      <x:c r="O23" s="9"/>
+      <x:c r="P23" s="9"/>
+    </x:row>
+    <x:row r="24" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A24" s="9"/>
+      <x:c r="B24" s="9"/>
+      <x:c r="C24" s="9"/>
+      <x:c r="D24" s="9"/>
+      <x:c r="E24" s="9"/>
+      <x:c r="F24" s="9"/>
+      <x:c r="G24" s="9"/>
+      <x:c r="H24" s="9"/>
+      <x:c r="I24" s="9"/>
+      <x:c r="J24" s="9"/>
+      <x:c r="K24" s="9"/>
+      <x:c r="L24" s="9"/>
+      <x:c r="M24" s="9"/>
+      <x:c r="N24" s="9"/>
+      <x:c r="O24" s="9"/>
+      <x:c r="P24" s="9"/>
+    </x:row>
+    <x:row r="25" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A25" s="9"/>
+      <x:c r="B25" s="9"/>
+      <x:c r="C25" s="9"/>
+      <x:c r="D25" s="9"/>
+      <x:c r="E25" s="9"/>
+      <x:c r="F25" s="9"/>
+      <x:c r="G25" s="9"/>
+      <x:c r="H25" s="9"/>
+      <x:c r="I25" s="9"/>
+      <x:c r="J25" s="9"/>
+      <x:c r="K25" s="9"/>
+      <x:c r="L25" s="9"/>
+      <x:c r="M25" s="9"/>
+      <x:c r="N25" s="9"/>
+      <x:c r="O25" s="9"/>
+      <x:c r="P25" s="9"/>
+    </x:row>
+    <x:row r="26" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A26" s="9"/>
+      <x:c r="B26" s="9"/>
+      <x:c r="C26" s="9"/>
+      <x:c r="D26" s="9"/>
+      <x:c r="E26" s="9"/>
+      <x:c r="F26" s="9"/>
+      <x:c r="G26" s="9"/>
+      <x:c r="H26" s="9"/>
+      <x:c r="I26" s="9"/>
+      <x:c r="J26" s="9"/>
+      <x:c r="K26" s="9"/>
+      <x:c r="L26" s="9"/>
+      <x:c r="M26" s="9"/>
+      <x:c r="N26" s="9"/>
+      <x:c r="O26" s="9"/>
+      <x:c r="P26" s="9"/>
+    </x:row>
+    <x:row r="27" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A27" s="9"/>
+      <x:c r="B27" s="9"/>
+      <x:c r="C27" s="9"/>
+      <x:c r="D27" s="9"/>
+      <x:c r="E27" s="9"/>
+      <x:c r="F27" s="9"/>
+      <x:c r="G27" s="9"/>
+      <x:c r="H27" s="9"/>
+      <x:c r="I27" s="9"/>
+      <x:c r="J27" s="9"/>
+      <x:c r="K27" s="9"/>
+      <x:c r="L27" s="9"/>
+      <x:c r="M27" s="9"/>
+      <x:c r="N27" s="9"/>
+      <x:c r="O27" s="9"/>
+      <x:c r="P27" s="9"/>
+    </x:row>
+    <x:row r="28" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A28" s="9"/>
+      <x:c r="B28" s="9"/>
+      <x:c r="C28" s="9"/>
+      <x:c r="D28" s="9"/>
+      <x:c r="E28" s="9"/>
+      <x:c r="F28" s="9"/>
+      <x:c r="G28" s="9"/>
+      <x:c r="H28" s="9"/>
+      <x:c r="I28" s="9"/>
+      <x:c r="J28" s="9"/>
+      <x:c r="K28" s="9"/>
+      <x:c r="L28" s="9"/>
+      <x:c r="M28" s="9"/>
+      <x:c r="N28" s="9"/>
+      <x:c r="O28" s="9"/>
+      <x:c r="P28" s="9"/>
+    </x:row>
+    <x:row r="29" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A29" s="10"/>
+      <x:c r="B29" s="10"/>
+      <x:c r="C29" s="10"/>
+      <x:c r="D29" s="10"/>
+      <x:c r="E29" s="10"/>
+      <x:c r="F29" s="10"/>
+      <x:c r="G29" s="10"/>
+      <x:c r="H29" s="10"/>
+      <x:c r="I29" s="10"/>
+      <x:c r="J29" s="10"/>
+      <x:c r="K29" s="10"/>
+      <x:c r="L29" s="10"/>
+      <x:c r="M29" s="10"/>
+      <x:c r="N29" s="10"/>
+      <x:c r="O29" s="10"/>
+      <x:c r="P29" s="10"/>
+    </x:row>
+    <x:row r="30" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A30" s="10"/>
+      <x:c r="B30" s="10"/>
+      <x:c r="C30" s="10"/>
+      <x:c r="D30" s="10"/>
+      <x:c r="E30" s="10"/>
+      <x:c r="F30" s="10"/>
+      <x:c r="G30" s="10"/>
+      <x:c r="H30" s="10"/>
+      <x:c r="I30" s="10"/>
+      <x:c r="J30" s="10"/>
+      <x:c r="K30" s="10"/>
+      <x:c r="L30" s="10"/>
+      <x:c r="M30" s="10"/>
+      <x:c r="N30" s="10"/>
+      <x:c r="O30" s="10"/>
+      <x:c r="P30" s="10"/>
+    </x:row>
+    <x:row r="31" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A31" s="10"/>
+      <x:c r="B31" s="10"/>
+      <x:c r="C31" s="10"/>
+      <x:c r="D31" s="10"/>
+      <x:c r="E31" s="10"/>
+      <x:c r="F31" s="10"/>
+      <x:c r="G31" s="10"/>
+      <x:c r="H31" s="10"/>
+      <x:c r="I31" s="10"/>
+      <x:c r="J31" s="10"/>
+      <x:c r="K31" s="10"/>
+      <x:c r="L31" s="10"/>
+      <x:c r="M31" s="10"/>
+      <x:c r="N31" s="10"/>
+      <x:c r="O31" s="10"/>
+      <x:c r="P31" s="10"/>
+    </x:row>
+    <x:row r="32" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A32" s="10"/>
+      <x:c r="B32" s="10"/>
+      <x:c r="C32" s="10"/>
+      <x:c r="D32" s="10"/>
+      <x:c r="E32" s="10"/>
+      <x:c r="F32" s="10"/>
+      <x:c r="G32" s="10"/>
+      <x:c r="H32" s="10"/>
+      <x:c r="I32" s="10"/>
+      <x:c r="J32" s="10"/>
+      <x:c r="K32" s="10"/>
+      <x:c r="L32" s="10"/>
+      <x:c r="M32" s="10"/>
+      <x:c r="N32" s="10"/>
+      <x:c r="O32" s="10"/>
+      <x:c r="P32" s="10"/>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1"/>
     <x:row r="34" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -21,151 +21,151 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
   <x:si>
+    <x:t>각성스킬 데미지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬애니메이션경로</x:t>
+  </x:si>
+  <x:si>
     <x:t>마법으로 만든 화살을 날린다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
   </x:si>
   <x:si>
-    <x:t>각성스킬 데미지</x:t>
+    <x:t>전방으로 불을 뿜는다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
   </x:si>
   <x:si>
     <x:t>스킬범위 안의 적들을 얼린다 (스킬 레벨이 증가할수록 얼어있는 시간이 늘어난다)</x:t>
   </x:si>
   <x:si>
-    <x:t>전방으로 불을 뿜는다 (스킬 레벨이 증가할수록 데미지가 증가하고 쿨타임이 감소한다)</x:t>
+    <x:t>가까운 적에게 번개를 쏜다 (스킬 레벨이 증가할수록 번개 줄기가 늘어난다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 지속시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamageInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimControllerPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_magicArrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_lightning_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolDownPerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각성스킬 쿨타임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anim/AnimController_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ice_01</x:t>
   </x:si>
   <x:si>
     <x:t>AwakedDamage</x:t>
   </x:si>
   <x:si>
-    <x:t>가까운 적에게 번개를 쏜다 (스킬 레벨이 증가할수록 번개 줄기가 늘어난다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬애니메이션경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_magicArrow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimControllerPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolDownPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_lightning_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDamageInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쿨타임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 지속시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
+    <x:t>SkillCoolTime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DamagePerLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AwakedCoolTime</x:t>
   </x:si>
   <x:si>
     <x:t>레벨당 줄어들 쿨타임 수치</x:t>
   </x:si>
   <x:si>
+    <x:t>SkillDuration</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레벨당 오를 데미지 수치</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_fire_01</x:t>
   </x:si>
   <x:si>
-    <x:t>DamagePerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDuration</x:t>
-  </x:si>
-  <x:si>
     <x:t>레벨당 오를 스킬 지속시간</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_ice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레벨당 오를 데미지 수치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Anim/AnimController_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
-  </x:si>
-  <x:si>
     <x:t>SkillDurationPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AwakedCoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>각성스킬 쿨타임</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -945,7 +945,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -953,151 +953,151 @@
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
       <x:c r="G1" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M1" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N1" s="2" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O1" s="2" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="M1" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="N1" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="O1" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="P1" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="O2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L3" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M3" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="N3" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="O3" s="3" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="s">
+      <x:c r="P3" s="3" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L3" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="M3" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="N3" s="3" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O3" s="3" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="P3" s="3" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E4" s="4">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>150</x:v>
@@ -1119,7 +1119,7 @@
       </x:c>
       <x:c r="N4" s="4"/>
       <x:c r="O4" s="4">
-        <x:v>0.10000000000000001</x:v>
+        <x:v>0.20000000000000001</x:v>
       </x:c>
       <x:c r="P4" s="4">
         <x:v>5000</x:v>
@@ -1127,16 +1127,16 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="5">
         <x:v>0</x:v>
@@ -1151,7 +1151,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J5" s="5">
         <x:v>1.5</x:v>
@@ -1165,9 +1165,11 @@
       <x:c r="M5" s="5">
         <x:v>0.29999999999999999</x:v>
       </x:c>
-      <x:c r="N5" s="5"/>
-      <x:c r="O5" s="5">
-        <x:v>5</x:v>
+      <x:c r="N5" s="5">
+        <x:v>0.10000000000000001</x:v>
+      </x:c>
+      <x:c r="O5" s="4">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P5" s="5">
         <x:v>3000</x:v>
@@ -1175,19 +1177,19 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E6" s="5">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="5">
         <x:v>100</x:v>
@@ -1209,11 +1211,9 @@
       <x:c r="M6" s="5">
         <x:v>0.20000000000000001</x:v>
       </x:c>
-      <x:c r="N6" s="5">
-        <x:v>0.20000000000000001</x:v>
-      </x:c>
-      <x:c r="O6" s="5">
-        <x:v>3</x:v>
+      <x:c r="N6" s="5"/>
+      <x:c r="O6" s="4">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="P6" s="5">
         <x:v>4000</x:v>
@@ -1221,16 +1221,16 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E7" s="6">
         <x:v>0</x:v>
@@ -1239,13 +1239,13 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="G7" s="6">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="6">
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J7" s="6"/>
       <x:c r="K7" s="6"/>
@@ -1256,8 +1256,8 @@
         <x:v>0.20000000000000001</x:v>
       </x:c>
       <x:c r="N7" s="6"/>
-      <x:c r="O7" s="6">
-        <x:v>2</x:v>
+      <x:c r="O7" s="4">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="P7" s="6">
         <x:v>5000</x:v>
